--- a/reports/集团总公司_现金流量表_2026-09.xlsx
+++ b/reports/集团总公司_现金流量表_2026-09.xlsx
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>210892500</v>
+        <v>206802874</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>1799953428</v>
+        <v>1769563684</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>4223625</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>36519992</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>2095700</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>18257404</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>1057576</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>9136172</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>837758</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>7298646</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>634287</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>5484135</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>419468</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>3648411</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>316436</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>2742151</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>210333</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>1824558</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>525731</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>4568442</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>265095</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>2293671</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>166689</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>1451570</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>573195</v>
+        <v>565376</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>4973149</v>
+        <v>4884708</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>3893400</v>
+        <v>3808190</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>33779880</v>
+        <v>33183812</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>215359095</v>
+        <v>221929138</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>129780000</v>
+        <v>127598262</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>1125996000</v>
+        <v>1107776327</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>1405215</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>12167868</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>1049387</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>9133010</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>704439</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>6088070</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>523700</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>4563359</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>352559</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>3045948</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>263207</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>2292230</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>26172300</v>
+        <v>25778688</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>227075860</v>
+        <v>223024539</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>12112800</v>
+        <v>11859722</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>105092960</v>
+        <v>103069195</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>5515650</v>
+        <v>5418527</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>47854830</v>
+        <v>46997923</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>173580750</v>
+        <v>174953706</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>41778345</v>
+        <v>46975432</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>247200</v>
+        <v>244095</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>2224800</v>
+        <v>2189325</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>2163000</v>
+        <v>2128844</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>19467000</v>
+        <v>19136569</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>1318400</v>
+        <v>1294040</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>11865600</v>
+        <v>11644379</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>2410200</v>
+        <v>2372939</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>20600000</v>
+        <v>20228435</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>185400000</v>
+        <v>181561302</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2987000</v>
+        <v>2913256</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>26883000</v>
+        <v>26314980</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3107,10 +3107,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>14626000</v>
+        <v>14400430</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>131634000</v>
+        <v>129066162</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3219,10 +3219,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>535600</v>
+        <v>527678</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>4820400</v>
+        <v>4739319</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>21135600</v>
+        <v>20756113</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-18725400</v>
+        <v>-18383174</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>4841000</v>
+        <v>4746427</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>43569000</v>
+        <v>42848860</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>7725000</v>
+        <v>7553910</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>69525000</v>
+        <v>68275415</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>7725000</v>
+        <v>7627947</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>69525000</v>
+        <v>68364759</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>247200</v>
+        <v>241853</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>2224800</v>
+        <v>2184784</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>12813200</v>
+        <v>12542190</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>6283000</v>
+        <v>6157923</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>56547000</v>
+        <v>55513456</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>6283000</v>
+        <v>6182976</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>56547000</v>
+        <v>55629475</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>1030000</v>
+        <v>1012322</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>9270000</v>
+        <v>9101162</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3597,10 +3597,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>896100</v>
+        <v>883380</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>8064900</v>
+        <v>7923803</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>128750</v>
+        <v>125955</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>1158750</v>
+        <v>1138186</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>7441750</v>
+        <v>7296200</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>5371450</v>
+        <v>5245990</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>28424395</v>
+        <v>33838248</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>28424395</v>
+        <v>33838248</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
